--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572663.438966978</v>
+        <v>572663</v>
       </c>
       <c r="R2" t="n">
-        <v>6367909.205483948</v>
+        <v>6367909</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-07-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-07-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31390-2025 artfynd.xlsx
+++ b/artfynd/A 31390-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469334</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
